--- a/artfynd/A 36011-2025 artfynd.xlsx
+++ b/artfynd/A 36011-2025 artfynd.xlsx
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127669042</v>
+        <v>127669035</v>
       </c>
       <c r="B5" t="n">
         <v>57661</v>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466580</v>
+        <v>467077</v>
       </c>
       <c r="R5" t="n">
-        <v>7057216</v>
+        <v>7057257</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127669035</v>
+        <v>127669042</v>
       </c>
       <c r="B6" t="n">
         <v>57661</v>
@@ -1118,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467077</v>
+        <v>466580</v>
       </c>
       <c r="R6" t="n">
-        <v>7057257</v>
+        <v>7057216</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127669021</v>
+        <v>127669036</v>
       </c>
       <c r="B8" t="n">
         <v>57661</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466659</v>
+        <v>466984</v>
       </c>
       <c r="R8" t="n">
-        <v>7057412</v>
+        <v>7057198</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1389,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127669036</v>
+        <v>127669021</v>
       </c>
       <c r="B9" t="n">
         <v>57661</v>
@@ -1424,10 +1424,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466984</v>
+        <v>466659</v>
       </c>
       <c r="R9" t="n">
-        <v>7057198</v>
+        <v>7057412</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127669039</v>
+        <v>127669044</v>
       </c>
       <c r="B10" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1502,21 +1502,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1526,10 +1526,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466611</v>
+        <v>466937</v>
       </c>
       <c r="R10" t="n">
-        <v>7057193</v>
+        <v>7057122</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1593,7 +1593,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127669030</v>
+        <v>127669039</v>
       </c>
       <c r="B11" t="n">
         <v>57661</v>
@@ -1628,10 +1628,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466857</v>
+        <v>466611</v>
       </c>
       <c r="R11" t="n">
-        <v>7057265</v>
+        <v>7057193</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127669044</v>
+        <v>127669030</v>
       </c>
       <c r="B12" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1706,21 +1706,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466937</v>
+        <v>466857</v>
       </c>
       <c r="R12" t="n">
-        <v>7057122</v>
+        <v>7057265</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1770,7 +1770,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2307,7 +2307,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127669027</v>
+        <v>127669032</v>
       </c>
       <c r="B18" t="n">
         <v>57661</v>
@@ -2342,10 +2342,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466891</v>
+        <v>467013</v>
       </c>
       <c r="R18" t="n">
-        <v>7057348</v>
+        <v>7057305</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2409,7 +2409,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127669032</v>
+        <v>127669027</v>
       </c>
       <c r="B19" t="n">
         <v>57661</v>
@@ -2444,10 +2444,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>467013</v>
+        <v>466891</v>
       </c>
       <c r="R19" t="n">
-        <v>7057305</v>
+        <v>7057348</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2511,7 +2511,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127669041</v>
+        <v>127669037</v>
       </c>
       <c r="B20" t="n">
         <v>57661</v>
@@ -2546,10 +2546,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466603</v>
+        <v>466828</v>
       </c>
       <c r="R20" t="n">
-        <v>7057208</v>
+        <v>7057181</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,7 +2613,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127669025</v>
+        <v>127669024</v>
       </c>
       <c r="B21" t="n">
         <v>57661</v>
@@ -2651,7 +2651,7 @@
         <v>466688</v>
       </c>
       <c r="R21" t="n">
-        <v>7057397</v>
+        <v>7057402</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2715,7 +2715,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127669024</v>
+        <v>127669041</v>
       </c>
       <c r="B22" t="n">
         <v>57661</v>
@@ -2750,10 +2750,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466688</v>
+        <v>466603</v>
       </c>
       <c r="R22" t="n">
-        <v>7057402</v>
+        <v>7057208</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2817,7 +2817,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127669037</v>
+        <v>127669025</v>
       </c>
       <c r="B23" t="n">
         <v>57661</v>
@@ -2852,10 +2852,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466828</v>
+        <v>466688</v>
       </c>
       <c r="R23" t="n">
-        <v>7057181</v>
+        <v>7057397</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2892,7 +2892,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 36011-2025 artfynd.xlsx
+++ b/artfynd/A 36011-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127669038</v>
       </c>
       <c r="B2" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>127669040</v>
       </c>
       <c r="B3" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>127669034</v>
       </c>
       <c r="B4" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>127669035</v>
       </c>
       <c r="B5" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>127669042</v>
       </c>
       <c r="B6" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>127669031</v>
       </c>
       <c r="B7" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127669036</v>
+        <v>127669021</v>
       </c>
       <c r="B8" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466984</v>
+        <v>466659</v>
       </c>
       <c r="R8" t="n">
-        <v>7057198</v>
+        <v>7057412</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127669021</v>
+        <v>127669036</v>
       </c>
       <c r="B9" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1424,10 +1424,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466659</v>
+        <v>466984</v>
       </c>
       <c r="R9" t="n">
-        <v>7057412</v>
+        <v>7057198</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127669044</v>
+        <v>127669039</v>
       </c>
       <c r="B10" t="n">
-        <v>79018</v>
+        <v>57663</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1502,21 +1502,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1526,10 +1526,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466937</v>
+        <v>466611</v>
       </c>
       <c r="R10" t="n">
-        <v>7057122</v>
+        <v>7057193</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127669039</v>
+        <v>127669030</v>
       </c>
       <c r="B11" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1628,10 +1628,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466611</v>
+        <v>466857</v>
       </c>
       <c r="R11" t="n">
-        <v>7057193</v>
+        <v>7057265</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127669030</v>
+        <v>127669044</v>
       </c>
       <c r="B12" t="n">
-        <v>57661</v>
+        <v>79020</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1706,21 +1706,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466857</v>
+        <v>466937</v>
       </c>
       <c r="R12" t="n">
-        <v>7057265</v>
+        <v>7057122</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1770,7 +1770,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1800,7 +1800,7 @@
         <v>127669029</v>
       </c>
       <c r="B13" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>127669020</v>
       </c>
       <c r="B14" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>127669023</v>
       </c>
       <c r="B15" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>127669043</v>
       </c>
       <c r="B16" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>127669028</v>
       </c>
       <c r="B17" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
         <v>127669032</v>
       </c>
       <c r="B18" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
         <v>127669027</v>
       </c>
       <c r="B19" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>127669037</v>
       </c>
       <c r="B20" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>127669024</v>
       </c>
       <c r="B21" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>127669041</v>
       </c>
       <c r="B22" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>127669025</v>
       </c>
       <c r="B23" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>127669022</v>
       </c>
       <c r="B24" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>127669033</v>
       </c>
       <c r="B25" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
         <v>127669026</v>
       </c>
       <c r="B26" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 36011-2025 artfynd.xlsx
+++ b/artfynd/A 36011-2025 artfynd.xlsx
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127669021</v>
+        <v>127669036</v>
       </c>
       <c r="B8" t="n">
         <v>57663</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466659</v>
+        <v>466984</v>
       </c>
       <c r="R8" t="n">
-        <v>7057412</v>
+        <v>7057198</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1389,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127669036</v>
+        <v>127669021</v>
       </c>
       <c r="B9" t="n">
         <v>57663</v>
@@ -1424,10 +1424,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466984</v>
+        <v>466659</v>
       </c>
       <c r="R9" t="n">
-        <v>7057198</v>
+        <v>7057412</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127669043</v>
+        <v>127669028</v>
       </c>
       <c r="B16" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2114,21 +2114,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2138,10 +2138,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467172</v>
+        <v>466893</v>
       </c>
       <c r="R16" t="n">
-        <v>7057297</v>
+        <v>7057337</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127669028</v>
+        <v>127669043</v>
       </c>
       <c r="B17" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2216,21 +2216,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466893</v>
+        <v>467172</v>
       </c>
       <c r="R17" t="n">
-        <v>7057337</v>
+        <v>7057297</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 36011-2025 artfynd.xlsx
+++ b/artfynd/A 36011-2025 artfynd.xlsx
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127669039</v>
+        <v>127669044</v>
       </c>
       <c r="B10" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1502,21 +1502,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1526,10 +1526,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466611</v>
+        <v>466937</v>
       </c>
       <c r="R10" t="n">
-        <v>7057193</v>
+        <v>7057122</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1593,7 +1593,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127669030</v>
+        <v>127669039</v>
       </c>
       <c r="B11" t="n">
         <v>57663</v>
@@ -1628,10 +1628,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466857</v>
+        <v>466611</v>
       </c>
       <c r="R11" t="n">
-        <v>7057265</v>
+        <v>7057193</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127669044</v>
+        <v>127669030</v>
       </c>
       <c r="B12" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1706,21 +1706,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466937</v>
+        <v>466857</v>
       </c>
       <c r="R12" t="n">
-        <v>7057122</v>
+        <v>7057265</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1770,7 +1770,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127669028</v>
+        <v>127669043</v>
       </c>
       <c r="B16" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2114,21 +2114,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2138,10 +2138,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466893</v>
+        <v>467172</v>
       </c>
       <c r="R16" t="n">
-        <v>7057337</v>
+        <v>7057297</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127669043</v>
+        <v>127669028</v>
       </c>
       <c r="B17" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2216,21 +2216,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467172</v>
+        <v>466893</v>
       </c>
       <c r="R17" t="n">
-        <v>7057297</v>
+        <v>7057337</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 36011-2025 artfynd.xlsx
+++ b/artfynd/A 36011-2025 artfynd.xlsx
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127669044</v>
+        <v>127669039</v>
       </c>
       <c r="B10" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1502,21 +1502,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1526,10 +1526,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466937</v>
+        <v>466611</v>
       </c>
       <c r="R10" t="n">
-        <v>7057122</v>
+        <v>7057193</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1593,7 +1593,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127669039</v>
+        <v>127669030</v>
       </c>
       <c r="B11" t="n">
         <v>57663</v>
@@ -1628,10 +1628,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466611</v>
+        <v>466857</v>
       </c>
       <c r="R11" t="n">
-        <v>7057193</v>
+        <v>7057265</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127669030</v>
+        <v>127669044</v>
       </c>
       <c r="B12" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1706,21 +1706,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466857</v>
+        <v>466937</v>
       </c>
       <c r="R12" t="n">
-        <v>7057265</v>
+        <v>7057122</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1770,7 +1770,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127669043</v>
+        <v>127669028</v>
       </c>
       <c r="B16" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2114,21 +2114,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2138,10 +2138,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467172</v>
+        <v>466893</v>
       </c>
       <c r="R16" t="n">
-        <v>7057297</v>
+        <v>7057337</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127669028</v>
+        <v>127669043</v>
       </c>
       <c r="B17" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2216,21 +2216,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466893</v>
+        <v>467172</v>
       </c>
       <c r="R17" t="n">
-        <v>7057337</v>
+        <v>7057297</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 36011-2025 artfynd.xlsx
+++ b/artfynd/A 36011-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127669038</v>
+        <v>127669040</v>
       </c>
       <c r="B2" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466664</v>
+        <v>466606</v>
       </c>
       <c r="R2" t="n">
-        <v>7057206</v>
+        <v>7057202</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127669040</v>
+        <v>127669038</v>
       </c>
       <c r="B3" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466606</v>
+        <v>466664</v>
       </c>
       <c r="R3" t="n">
-        <v>7057202</v>
+        <v>7057206</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,7 +882,7 @@
         <v>127669034</v>
       </c>
       <c r="B4" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>127669035</v>
       </c>
       <c r="B5" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>127669042</v>
       </c>
       <c r="B6" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>127669031</v>
       </c>
       <c r="B7" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>127669036</v>
       </c>
       <c r="B8" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>127669021</v>
       </c>
       <c r="B9" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127669039</v>
+        <v>127669030</v>
       </c>
       <c r="B10" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1526,10 +1526,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466611</v>
+        <v>466857</v>
       </c>
       <c r="R10" t="n">
-        <v>7057193</v>
+        <v>7057265</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127669030</v>
+        <v>127669044</v>
       </c>
       <c r="B11" t="n">
-        <v>57663</v>
+        <v>79023</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1604,21 +1604,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1628,10 +1628,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466857</v>
+        <v>466937</v>
       </c>
       <c r="R11" t="n">
-        <v>7057265</v>
+        <v>7057122</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127669044</v>
+        <v>127669039</v>
       </c>
       <c r="B12" t="n">
-        <v>79020</v>
+        <v>57666</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1706,21 +1706,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466937</v>
+        <v>466611</v>
       </c>
       <c r="R12" t="n">
-        <v>7057122</v>
+        <v>7057193</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1770,7 +1770,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1800,7 +1800,7 @@
         <v>127669029</v>
       </c>
       <c r="B13" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>127669020</v>
       </c>
       <c r="B14" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>127669023</v>
       </c>
       <c r="B15" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127669028</v>
+        <v>127669043</v>
       </c>
       <c r="B16" t="n">
-        <v>57663</v>
+        <v>79023</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2114,21 +2114,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2138,10 +2138,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466893</v>
+        <v>467172</v>
       </c>
       <c r="R16" t="n">
-        <v>7057337</v>
+        <v>7057297</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127669043</v>
+        <v>127669028</v>
       </c>
       <c r="B17" t="n">
-        <v>79020</v>
+        <v>57666</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2216,21 +2216,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467172</v>
+        <v>466893</v>
       </c>
       <c r="R17" t="n">
-        <v>7057297</v>
+        <v>7057337</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2310,7 +2310,7 @@
         <v>127669032</v>
       </c>
       <c r="B18" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
         <v>127669027</v>
       </c>
       <c r="B19" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127669037</v>
+        <v>127669024</v>
       </c>
       <c r="B20" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2546,10 +2546,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466828</v>
+        <v>466688</v>
       </c>
       <c r="R20" t="n">
-        <v>7057181</v>
+        <v>7057402</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2613,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127669024</v>
+        <v>127669037</v>
       </c>
       <c r="B21" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2648,10 +2648,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466688</v>
+        <v>466828</v>
       </c>
       <c r="R21" t="n">
-        <v>7057402</v>
+        <v>7057181</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2718,7 +2718,7 @@
         <v>127669041</v>
       </c>
       <c r="B22" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>127669025</v>
       </c>
       <c r="B23" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>127669022</v>
       </c>
       <c r="B24" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>127669033</v>
       </c>
       <c r="B25" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
         <v>127669026</v>
       </c>
       <c r="B26" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 36011-2025 artfynd.xlsx
+++ b/artfynd/A 36011-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127669040</v>
+        <v>127669038</v>
       </c>
       <c r="B2" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466606</v>
+        <v>466664</v>
       </c>
       <c r="R2" t="n">
-        <v>7057202</v>
+        <v>7057206</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127669038</v>
+        <v>127669040</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466664</v>
+        <v>466606</v>
       </c>
       <c r="R3" t="n">
-        <v>7057206</v>
+        <v>7057202</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,7 +882,7 @@
         <v>127669034</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>127669035</v>
       </c>
       <c r="B5" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>127669042</v>
       </c>
       <c r="B6" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>127669031</v>
       </c>
       <c r="B7" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127669036</v>
+        <v>127669021</v>
       </c>
       <c r="B8" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466984</v>
+        <v>466659</v>
       </c>
       <c r="R8" t="n">
-        <v>7057198</v>
+        <v>7057412</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127669021</v>
+        <v>127669036</v>
       </c>
       <c r="B9" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1424,10 +1424,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466659</v>
+        <v>466984</v>
       </c>
       <c r="R9" t="n">
-        <v>7057412</v>
+        <v>7057198</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127669030</v>
+        <v>127669044</v>
       </c>
       <c r="B10" t="n">
-        <v>57666</v>
+        <v>79029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1502,21 +1502,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1526,10 +1526,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466857</v>
+        <v>466937</v>
       </c>
       <c r="R10" t="n">
-        <v>7057265</v>
+        <v>7057122</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127669044</v>
+        <v>127669030</v>
       </c>
       <c r="B11" t="n">
-        <v>79023</v>
+        <v>57672</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1604,21 +1604,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1628,10 +1628,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466937</v>
+        <v>466857</v>
       </c>
       <c r="R11" t="n">
-        <v>7057122</v>
+        <v>7057265</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1698,7 +1698,7 @@
         <v>127669039</v>
       </c>
       <c r="B12" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>127669029</v>
       </c>
       <c r="B13" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>127669020</v>
       </c>
       <c r="B14" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>127669023</v>
       </c>
       <c r="B15" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>127669043</v>
       </c>
       <c r="B16" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>127669028</v>
       </c>
       <c r="B17" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2307,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127669032</v>
+        <v>127669027</v>
       </c>
       <c r="B18" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2342,10 +2342,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>467013</v>
+        <v>466891</v>
       </c>
       <c r="R18" t="n">
-        <v>7057305</v>
+        <v>7057348</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127669027</v>
+        <v>127669032</v>
       </c>
       <c r="B19" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2444,10 +2444,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466891</v>
+        <v>467013</v>
       </c>
       <c r="R19" t="n">
-        <v>7057348</v>
+        <v>7057305</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2511,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127669024</v>
+        <v>127669037</v>
       </c>
       <c r="B20" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2546,10 +2546,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466688</v>
+        <v>466828</v>
       </c>
       <c r="R20" t="n">
-        <v>7057402</v>
+        <v>7057181</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2613,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127669037</v>
+        <v>127669024</v>
       </c>
       <c r="B21" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2648,10 +2648,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466828</v>
+        <v>466688</v>
       </c>
       <c r="R21" t="n">
-        <v>7057181</v>
+        <v>7057402</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2718,7 +2718,7 @@
         <v>127669041</v>
       </c>
       <c r="B22" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>127669025</v>
       </c>
       <c r="B23" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>127669022</v>
       </c>
       <c r="B24" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>127669033</v>
       </c>
       <c r="B25" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
         <v>127669026</v>
       </c>
       <c r="B26" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 36011-2025 artfynd.xlsx
+++ b/artfynd/A 36011-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127669038</v>
+        <v>127669040</v>
       </c>
       <c r="B2" t="n">
         <v>57672</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466664</v>
+        <v>466606</v>
       </c>
       <c r="R2" t="n">
-        <v>7057206</v>
+        <v>7057202</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127669040</v>
+        <v>127669038</v>
       </c>
       <c r="B3" t="n">
         <v>57672</v>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466606</v>
+        <v>466664</v>
       </c>
       <c r="R3" t="n">
-        <v>7057202</v>
+        <v>7057206</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127669021</v>
+        <v>127669036</v>
       </c>
       <c r="B8" t="n">
         <v>57672</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466659</v>
+        <v>466984</v>
       </c>
       <c r="R8" t="n">
-        <v>7057412</v>
+        <v>7057198</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1389,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127669036</v>
+        <v>127669021</v>
       </c>
       <c r="B9" t="n">
         <v>57672</v>
@@ -1424,10 +1424,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466984</v>
+        <v>466659</v>
       </c>
       <c r="R9" t="n">
-        <v>7057198</v>
+        <v>7057412</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1593,7 +1593,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127669030</v>
+        <v>127669039</v>
       </c>
       <c r="B11" t="n">
         <v>57672</v>
@@ -1628,10 +1628,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466857</v>
+        <v>466611</v>
       </c>
       <c r="R11" t="n">
-        <v>7057265</v>
+        <v>7057193</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127669039</v>
+        <v>127669030</v>
       </c>
       <c r="B12" t="n">
         <v>57672</v>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466611</v>
+        <v>466857</v>
       </c>
       <c r="R12" t="n">
-        <v>7057193</v>
+        <v>7057265</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2307,7 +2307,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127669027</v>
+        <v>127669032</v>
       </c>
       <c r="B18" t="n">
         <v>57672</v>
@@ -2342,10 +2342,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466891</v>
+        <v>467013</v>
       </c>
       <c r="R18" t="n">
-        <v>7057348</v>
+        <v>7057305</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2409,7 +2409,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127669032</v>
+        <v>127669027</v>
       </c>
       <c r="B19" t="n">
         <v>57672</v>
@@ -2444,10 +2444,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>467013</v>
+        <v>466891</v>
       </c>
       <c r="R19" t="n">
-        <v>7057305</v>
+        <v>7057348</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2511,7 +2511,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127669037</v>
+        <v>127669025</v>
       </c>
       <c r="B20" t="n">
         <v>57672</v>
@@ -2546,10 +2546,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466828</v>
+        <v>466688</v>
       </c>
       <c r="R20" t="n">
-        <v>7057181</v>
+        <v>7057397</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2715,7 +2715,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127669041</v>
+        <v>127669037</v>
       </c>
       <c r="B22" t="n">
         <v>57672</v>
@@ -2750,10 +2750,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466603</v>
+        <v>466828</v>
       </c>
       <c r="R22" t="n">
-        <v>7057208</v>
+        <v>7057181</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,7 +2817,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127669025</v>
+        <v>127669041</v>
       </c>
       <c r="B23" t="n">
         <v>57672</v>
@@ -2852,10 +2852,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466688</v>
+        <v>466603</v>
       </c>
       <c r="R23" t="n">
-        <v>7057397</v>
+        <v>7057208</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2892,7 +2892,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 36011-2025 artfynd.xlsx
+++ b/artfynd/A 36011-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127669040</v>
+        <v>127669038</v>
       </c>
       <c r="B2" t="n">
         <v>57672</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466606</v>
+        <v>466664</v>
       </c>
       <c r="R2" t="n">
-        <v>7057202</v>
+        <v>7057206</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127669038</v>
+        <v>127669040</v>
       </c>
       <c r="B3" t="n">
         <v>57672</v>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466664</v>
+        <v>466606</v>
       </c>
       <c r="R3" t="n">
-        <v>7057206</v>
+        <v>7057202</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127669044</v>
+        <v>127669039</v>
       </c>
       <c r="B10" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1502,21 +1502,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1526,10 +1526,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466937</v>
+        <v>466611</v>
       </c>
       <c r="R10" t="n">
-        <v>7057122</v>
+        <v>7057193</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1593,7 +1593,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127669039</v>
+        <v>127669030</v>
       </c>
       <c r="B11" t="n">
         <v>57672</v>
@@ -1628,10 +1628,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466611</v>
+        <v>466857</v>
       </c>
       <c r="R11" t="n">
-        <v>7057193</v>
+        <v>7057265</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127669030</v>
+        <v>127669044</v>
       </c>
       <c r="B12" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1706,21 +1706,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466857</v>
+        <v>466937</v>
       </c>
       <c r="R12" t="n">
-        <v>7057265</v>
+        <v>7057122</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1770,7 +1770,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2511,7 +2511,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127669025</v>
+        <v>127669037</v>
       </c>
       <c r="B20" t="n">
         <v>57672</v>
@@ -2546,10 +2546,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466688</v>
+        <v>466828</v>
       </c>
       <c r="R20" t="n">
-        <v>7057397</v>
+        <v>7057181</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2715,7 +2715,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127669037</v>
+        <v>127669041</v>
       </c>
       <c r="B22" t="n">
         <v>57672</v>
@@ -2750,10 +2750,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466828</v>
+        <v>466603</v>
       </c>
       <c r="R22" t="n">
-        <v>7057181</v>
+        <v>7057208</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,7 +2817,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127669041</v>
+        <v>127669025</v>
       </c>
       <c r="B23" t="n">
         <v>57672</v>
@@ -2852,10 +2852,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466603</v>
+        <v>466688</v>
       </c>
       <c r="R23" t="n">
-        <v>7057208</v>
+        <v>7057397</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2892,7 +2892,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 36011-2025 artfynd.xlsx
+++ b/artfynd/A 36011-2025 artfynd.xlsx
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127669039</v>
+        <v>127669044</v>
       </c>
       <c r="B10" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1502,21 +1502,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1526,10 +1526,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466611</v>
+        <v>466937</v>
       </c>
       <c r="R10" t="n">
-        <v>7057193</v>
+        <v>7057122</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1593,7 +1593,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127669030</v>
+        <v>127669039</v>
       </c>
       <c r="B11" t="n">
         <v>57672</v>
@@ -1628,10 +1628,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466857</v>
+        <v>466611</v>
       </c>
       <c r="R11" t="n">
-        <v>7057265</v>
+        <v>7057193</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127669044</v>
+        <v>127669030</v>
       </c>
       <c r="B12" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1706,21 +1706,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466937</v>
+        <v>466857</v>
       </c>
       <c r="R12" t="n">
-        <v>7057122</v>
+        <v>7057265</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1770,7 +1770,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 36011-2025 artfynd.xlsx
+++ b/artfynd/A 36011-2025 artfynd.xlsx
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127669044</v>
+        <v>127669039</v>
       </c>
       <c r="B10" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1502,21 +1502,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1526,10 +1526,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466937</v>
+        <v>466611</v>
       </c>
       <c r="R10" t="n">
-        <v>7057122</v>
+        <v>7057193</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1593,7 +1593,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127669039</v>
+        <v>127669030</v>
       </c>
       <c r="B11" t="n">
         <v>57672</v>
@@ -1628,10 +1628,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466611</v>
+        <v>466857</v>
       </c>
       <c r="R11" t="n">
-        <v>7057193</v>
+        <v>7057265</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127669030</v>
+        <v>127669044</v>
       </c>
       <c r="B12" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1706,21 +1706,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466857</v>
+        <v>466937</v>
       </c>
       <c r="R12" t="n">
-        <v>7057265</v>
+        <v>7057122</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1770,7 +1770,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127669043</v>
+        <v>127669028</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2114,21 +2114,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2138,10 +2138,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467172</v>
+        <v>466893</v>
       </c>
       <c r="R16" t="n">
-        <v>7057297</v>
+        <v>7057337</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127669028</v>
+        <v>127669043</v>
       </c>
       <c r="B17" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2216,21 +2216,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466893</v>
+        <v>467172</v>
       </c>
       <c r="R17" t="n">
-        <v>7057337</v>
+        <v>7057297</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2511,7 +2511,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127669037</v>
+        <v>127669025</v>
       </c>
       <c r="B20" t="n">
         <v>57672</v>
@@ -2546,10 +2546,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466828</v>
+        <v>466688</v>
       </c>
       <c r="R20" t="n">
-        <v>7057181</v>
+        <v>7057397</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2613,7 +2613,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127669024</v>
+        <v>127669037</v>
       </c>
       <c r="B21" t="n">
         <v>57672</v>
@@ -2648,10 +2648,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466688</v>
+        <v>466828</v>
       </c>
       <c r="R21" t="n">
-        <v>7057402</v>
+        <v>7057181</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2715,7 +2715,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127669041</v>
+        <v>127669024</v>
       </c>
       <c r="B22" t="n">
         <v>57672</v>
@@ -2750,10 +2750,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466603</v>
+        <v>466688</v>
       </c>
       <c r="R22" t="n">
-        <v>7057208</v>
+        <v>7057402</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2817,7 +2817,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127669025</v>
+        <v>127669041</v>
       </c>
       <c r="B23" t="n">
         <v>57672</v>
@@ -2852,10 +2852,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466688</v>
+        <v>466603</v>
       </c>
       <c r="R23" t="n">
-        <v>7057397</v>
+        <v>7057208</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2892,7 +2892,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 36011-2025 artfynd.xlsx
+++ b/artfynd/A 36011-2025 artfynd.xlsx
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127669028</v>
+        <v>127669043</v>
       </c>
       <c r="B16" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2114,21 +2114,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2138,10 +2138,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466893</v>
+        <v>467172</v>
       </c>
       <c r="R16" t="n">
-        <v>7057337</v>
+        <v>7057297</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127669043</v>
+        <v>127669028</v>
       </c>
       <c r="B17" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2216,21 +2216,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467172</v>
+        <v>466893</v>
       </c>
       <c r="R17" t="n">
-        <v>7057297</v>
+        <v>7057337</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2511,7 +2511,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127669025</v>
+        <v>127669041</v>
       </c>
       <c r="B20" t="n">
         <v>57672</v>
@@ -2546,10 +2546,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466688</v>
+        <v>466603</v>
       </c>
       <c r="R20" t="n">
-        <v>7057397</v>
+        <v>7057208</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2613,7 +2613,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127669037</v>
+        <v>127669025</v>
       </c>
       <c r="B21" t="n">
         <v>57672</v>
@@ -2648,10 +2648,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466828</v>
+        <v>466688</v>
       </c>
       <c r="R21" t="n">
-        <v>7057181</v>
+        <v>7057397</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2715,7 +2715,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127669024</v>
+        <v>127669037</v>
       </c>
       <c r="B22" t="n">
         <v>57672</v>
@@ -2750,10 +2750,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466688</v>
+        <v>466828</v>
       </c>
       <c r="R22" t="n">
-        <v>7057402</v>
+        <v>7057181</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2817,7 +2817,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127669041</v>
+        <v>127669024</v>
       </c>
       <c r="B23" t="n">
         <v>57672</v>
@@ -2852,10 +2852,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466603</v>
+        <v>466688</v>
       </c>
       <c r="R23" t="n">
-        <v>7057208</v>
+        <v>7057402</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2892,7 +2892,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 36011-2025 artfynd.xlsx
+++ b/artfynd/A 36011-2025 artfynd.xlsx
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127669039</v>
+        <v>127669044</v>
       </c>
       <c r="B10" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1502,21 +1502,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1526,10 +1526,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466611</v>
+        <v>466937</v>
       </c>
       <c r="R10" t="n">
-        <v>7057193</v>
+        <v>7057122</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1593,7 +1593,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127669030</v>
+        <v>127669039</v>
       </c>
       <c r="B11" t="n">
         <v>57672</v>
@@ -1628,10 +1628,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466857</v>
+        <v>466611</v>
       </c>
       <c r="R11" t="n">
-        <v>7057265</v>
+        <v>7057193</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127669044</v>
+        <v>127669030</v>
       </c>
       <c r="B12" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1706,21 +1706,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466937</v>
+        <v>466857</v>
       </c>
       <c r="R12" t="n">
-        <v>7057122</v>
+        <v>7057265</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1770,7 +1770,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2511,7 +2511,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127669041</v>
+        <v>127669037</v>
       </c>
       <c r="B20" t="n">
         <v>57672</v>
@@ -2546,10 +2546,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466603</v>
+        <v>466828</v>
       </c>
       <c r="R20" t="n">
-        <v>7057208</v>
+        <v>7057181</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,7 +2613,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127669025</v>
+        <v>127669024</v>
       </c>
       <c r="B21" t="n">
         <v>57672</v>
@@ -2651,7 +2651,7 @@
         <v>466688</v>
       </c>
       <c r="R21" t="n">
-        <v>7057397</v>
+        <v>7057402</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2715,7 +2715,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127669037</v>
+        <v>127669041</v>
       </c>
       <c r="B22" t="n">
         <v>57672</v>
@@ -2750,10 +2750,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466828</v>
+        <v>466603</v>
       </c>
       <c r="R22" t="n">
-        <v>7057181</v>
+        <v>7057208</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,7 +2817,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127669024</v>
+        <v>127669025</v>
       </c>
       <c r="B23" t="n">
         <v>57672</v>
@@ -2855,7 +2855,7 @@
         <v>466688</v>
       </c>
       <c r="R23" t="n">
-        <v>7057402</v>
+        <v>7057397</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2892,7 +2892,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 36011-2025 artfynd.xlsx
+++ b/artfynd/A 36011-2025 artfynd.xlsx
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127669044</v>
+        <v>127669039</v>
       </c>
       <c r="B10" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1502,21 +1502,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1526,10 +1526,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466937</v>
+        <v>466611</v>
       </c>
       <c r="R10" t="n">
-        <v>7057122</v>
+        <v>7057193</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1593,7 +1593,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127669039</v>
+        <v>127669030</v>
       </c>
       <c r="B11" t="n">
         <v>57672</v>
@@ -1628,10 +1628,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466611</v>
+        <v>466857</v>
       </c>
       <c r="R11" t="n">
-        <v>7057193</v>
+        <v>7057265</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127669030</v>
+        <v>127669044</v>
       </c>
       <c r="B12" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1706,21 +1706,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466857</v>
+        <v>466937</v>
       </c>
       <c r="R12" t="n">
-        <v>7057265</v>
+        <v>7057122</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1770,7 +1770,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 36011-2025 artfynd.xlsx
+++ b/artfynd/A 36011-2025 artfynd.xlsx
@@ -2307,7 +2307,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127669032</v>
+        <v>127669027</v>
       </c>
       <c r="B18" t="n">
         <v>57672</v>
@@ -2342,10 +2342,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>467013</v>
+        <v>466891</v>
       </c>
       <c r="R18" t="n">
-        <v>7057305</v>
+        <v>7057348</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2409,7 +2409,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127669027</v>
+        <v>127669032</v>
       </c>
       <c r="B19" t="n">
         <v>57672</v>
@@ -2444,10 +2444,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466891</v>
+        <v>467013</v>
       </c>
       <c r="R19" t="n">
-        <v>7057348</v>
+        <v>7057305</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 36011-2025 artfynd.xlsx
+++ b/artfynd/A 36011-2025 artfynd.xlsx
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127669039</v>
+        <v>127669044</v>
       </c>
       <c r="B10" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1502,21 +1502,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1526,10 +1526,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466611</v>
+        <v>466937</v>
       </c>
       <c r="R10" t="n">
-        <v>7057193</v>
+        <v>7057122</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1593,7 +1593,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127669030</v>
+        <v>127669039</v>
       </c>
       <c r="B11" t="n">
         <v>57672</v>
@@ -1628,10 +1628,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466857</v>
+        <v>466611</v>
       </c>
       <c r="R11" t="n">
-        <v>7057265</v>
+        <v>7057193</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127669044</v>
+        <v>127669030</v>
       </c>
       <c r="B12" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1706,21 +1706,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466937</v>
+        <v>466857</v>
       </c>
       <c r="R12" t="n">
-        <v>7057122</v>
+        <v>7057265</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1770,7 +1770,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2511,7 +2511,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127669037</v>
+        <v>127669041</v>
       </c>
       <c r="B20" t="n">
         <v>57672</v>
@@ -2546,10 +2546,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466828</v>
+        <v>466603</v>
       </c>
       <c r="R20" t="n">
-        <v>7057181</v>
+        <v>7057208</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,7 +2613,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127669024</v>
+        <v>127669025</v>
       </c>
       <c r="B21" t="n">
         <v>57672</v>
@@ -2651,7 +2651,7 @@
         <v>466688</v>
       </c>
       <c r="R21" t="n">
-        <v>7057402</v>
+        <v>7057397</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2715,7 +2715,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127669041</v>
+        <v>127669037</v>
       </c>
       <c r="B22" t="n">
         <v>57672</v>
@@ -2750,10 +2750,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466603</v>
+        <v>466828</v>
       </c>
       <c r="R22" t="n">
-        <v>7057208</v>
+        <v>7057181</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,7 +2817,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127669025</v>
+        <v>127669024</v>
       </c>
       <c r="B23" t="n">
         <v>57672</v>
@@ -2855,7 +2855,7 @@
         <v>466688</v>
       </c>
       <c r="R23" t="n">
-        <v>7057397</v>
+        <v>7057402</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2892,7 +2892,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 36011-2025 artfynd.xlsx
+++ b/artfynd/A 36011-2025 artfynd.xlsx
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127669044</v>
+        <v>127669039</v>
       </c>
       <c r="B10" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1502,21 +1502,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1526,10 +1526,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466937</v>
+        <v>466611</v>
       </c>
       <c r="R10" t="n">
-        <v>7057122</v>
+        <v>7057193</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1593,7 +1593,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127669039</v>
+        <v>127669030</v>
       </c>
       <c r="B11" t="n">
         <v>57672</v>
@@ -1628,10 +1628,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466611</v>
+        <v>466857</v>
       </c>
       <c r="R11" t="n">
-        <v>7057193</v>
+        <v>7057265</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127669030</v>
+        <v>127669044</v>
       </c>
       <c r="B12" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1706,21 +1706,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466857</v>
+        <v>466937</v>
       </c>
       <c r="R12" t="n">
-        <v>7057265</v>
+        <v>7057122</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1770,7 +1770,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2307,7 +2307,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127669027</v>
+        <v>127669032</v>
       </c>
       <c r="B18" t="n">
         <v>57672</v>
@@ -2342,10 +2342,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466891</v>
+        <v>467013</v>
       </c>
       <c r="R18" t="n">
-        <v>7057348</v>
+        <v>7057305</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2409,7 +2409,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127669032</v>
+        <v>127669027</v>
       </c>
       <c r="B19" t="n">
         <v>57672</v>
@@ -2444,10 +2444,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>467013</v>
+        <v>466891</v>
       </c>
       <c r="R19" t="n">
-        <v>7057305</v>
+        <v>7057348</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2511,7 +2511,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127669041</v>
+        <v>127669037</v>
       </c>
       <c r="B20" t="n">
         <v>57672</v>
@@ -2546,10 +2546,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466603</v>
+        <v>466828</v>
       </c>
       <c r="R20" t="n">
-        <v>7057208</v>
+        <v>7057181</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,7 +2613,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127669025</v>
+        <v>127669024</v>
       </c>
       <c r="B21" t="n">
         <v>57672</v>
@@ -2651,7 +2651,7 @@
         <v>466688</v>
       </c>
       <c r="R21" t="n">
-        <v>7057397</v>
+        <v>7057402</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2715,7 +2715,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127669037</v>
+        <v>127669041</v>
       </c>
       <c r="B22" t="n">
         <v>57672</v>
@@ -2750,10 +2750,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466828</v>
+        <v>466603</v>
       </c>
       <c r="R22" t="n">
-        <v>7057181</v>
+        <v>7057208</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,7 +2817,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127669024</v>
+        <v>127669025</v>
       </c>
       <c r="B23" t="n">
         <v>57672</v>
@@ -2855,7 +2855,7 @@
         <v>466688</v>
       </c>
       <c r="R23" t="n">
-        <v>7057402</v>
+        <v>7057397</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2892,7 +2892,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 36011-2025 artfynd.xlsx
+++ b/artfynd/A 36011-2025 artfynd.xlsx
@@ -2307,7 +2307,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127669032</v>
+        <v>127669027</v>
       </c>
       <c r="B18" t="n">
         <v>57672</v>
@@ -2342,10 +2342,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>467013</v>
+        <v>466891</v>
       </c>
       <c r="R18" t="n">
-        <v>7057305</v>
+        <v>7057348</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2409,7 +2409,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127669027</v>
+        <v>127669032</v>
       </c>
       <c r="B19" t="n">
         <v>57672</v>
@@ -2444,10 +2444,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466891</v>
+        <v>467013</v>
       </c>
       <c r="R19" t="n">
-        <v>7057348</v>
+        <v>7057305</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2511,7 +2511,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127669037</v>
+        <v>127669041</v>
       </c>
       <c r="B20" t="n">
         <v>57672</v>
@@ -2546,10 +2546,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466828</v>
+        <v>466603</v>
       </c>
       <c r="R20" t="n">
-        <v>7057181</v>
+        <v>7057208</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,7 +2613,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127669024</v>
+        <v>127669025</v>
       </c>
       <c r="B21" t="n">
         <v>57672</v>
@@ -2651,7 +2651,7 @@
         <v>466688</v>
       </c>
       <c r="R21" t="n">
-        <v>7057402</v>
+        <v>7057397</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2715,7 +2715,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127669041</v>
+        <v>127669037</v>
       </c>
       <c r="B22" t="n">
         <v>57672</v>
@@ -2750,10 +2750,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466603</v>
+        <v>466828</v>
       </c>
       <c r="R22" t="n">
-        <v>7057208</v>
+        <v>7057181</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,7 +2817,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127669025</v>
+        <v>127669024</v>
       </c>
       <c r="B23" t="n">
         <v>57672</v>
@@ -2855,7 +2855,7 @@
         <v>466688</v>
       </c>
       <c r="R23" t="n">
-        <v>7057397</v>
+        <v>7057402</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2892,7 +2892,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 36011-2025 artfynd.xlsx
+++ b/artfynd/A 36011-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127669038</v>
       </c>
       <c r="B2" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>127669040</v>
       </c>
       <c r="B3" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>127669034</v>
       </c>
       <c r="B4" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>127669035</v>
       </c>
       <c r="B5" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>127669042</v>
       </c>
       <c r="B6" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>127669031</v>
       </c>
       <c r="B7" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>127669036</v>
       </c>
       <c r="B8" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>127669021</v>
       </c>
       <c r="B9" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127669039</v>
+        <v>127669044</v>
       </c>
       <c r="B10" t="n">
-        <v>57672</v>
+        <v>79032</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1502,21 +1502,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1526,10 +1526,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466611</v>
+        <v>466937</v>
       </c>
       <c r="R10" t="n">
-        <v>7057193</v>
+        <v>7057122</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127669030</v>
+        <v>127669039</v>
       </c>
       <c r="B11" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1628,10 +1628,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466857</v>
+        <v>466611</v>
       </c>
       <c r="R11" t="n">
-        <v>7057265</v>
+        <v>7057193</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127669044</v>
+        <v>127669030</v>
       </c>
       <c r="B12" t="n">
-        <v>79029</v>
+        <v>57673</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1706,21 +1706,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466937</v>
+        <v>466857</v>
       </c>
       <c r="R12" t="n">
-        <v>7057122</v>
+        <v>7057265</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1770,7 +1770,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1800,7 +1800,7 @@
         <v>127669029</v>
       </c>
       <c r="B13" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>127669020</v>
       </c>
       <c r="B14" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>127669023</v>
       </c>
       <c r="B15" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>127669043</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>127669028</v>
       </c>
       <c r="B17" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2307,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127669027</v>
+        <v>127669032</v>
       </c>
       <c r="B18" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2342,10 +2342,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466891</v>
+        <v>467013</v>
       </c>
       <c r="R18" t="n">
-        <v>7057348</v>
+        <v>7057305</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127669032</v>
+        <v>127669027</v>
       </c>
       <c r="B19" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2444,10 +2444,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>467013</v>
+        <v>466891</v>
       </c>
       <c r="R19" t="n">
-        <v>7057305</v>
+        <v>7057348</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2511,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127669041</v>
+        <v>127669037</v>
       </c>
       <c r="B20" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2546,10 +2546,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466603</v>
+        <v>466828</v>
       </c>
       <c r="R20" t="n">
-        <v>7057208</v>
+        <v>7057181</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127669025</v>
+        <v>127669024</v>
       </c>
       <c r="B21" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         <v>466688</v>
       </c>
       <c r="R21" t="n">
-        <v>7057397</v>
+        <v>7057402</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2715,10 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127669037</v>
+        <v>127669041</v>
       </c>
       <c r="B22" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2750,10 +2750,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466828</v>
+        <v>466603</v>
       </c>
       <c r="R22" t="n">
-        <v>7057181</v>
+        <v>7057208</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127669024</v>
+        <v>127669025</v>
       </c>
       <c r="B23" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2855,7 +2855,7 @@
         <v>466688</v>
       </c>
       <c r="R23" t="n">
-        <v>7057402</v>
+        <v>7057397</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2892,7 +2892,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2922,7 +2922,7 @@
         <v>127669022</v>
       </c>
       <c r="B24" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>127669033</v>
       </c>
       <c r="B25" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
         <v>127669026</v>
       </c>
       <c r="B26" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 36011-2025 artfynd.xlsx
+++ b/artfynd/A 36011-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127669038</v>
+        <v>127669043</v>
       </c>
       <c r="B2" t="n">
-        <v>57673</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466664</v>
+        <v>467172</v>
       </c>
       <c r="R2" t="n">
-        <v>7057206</v>
+        <v>7057297</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127669040</v>
+        <v>127669044</v>
       </c>
       <c r="B3" t="n">
-        <v>57673</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466606</v>
+        <v>466937</v>
       </c>
       <c r="R3" t="n">
-        <v>7057202</v>
+        <v>7057122</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127669034</v>
+        <v>127669020</v>
       </c>
       <c r="B4" t="n">
-        <v>57673</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467117</v>
+        <v>466669</v>
       </c>
       <c r="R4" t="n">
-        <v>7057269</v>
+        <v>7057344</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127669035</v>
+        <v>127669021</v>
       </c>
       <c r="B5" t="n">
-        <v>57673</v>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467077</v>
+        <v>466659</v>
       </c>
       <c r="R5" t="n">
-        <v>7057257</v>
+        <v>7057412</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127669042</v>
+        <v>127669022</v>
       </c>
       <c r="B6" t="n">
-        <v>57673</v>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1118,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466580</v>
+        <v>466685</v>
       </c>
       <c r="R6" t="n">
-        <v>7057216</v>
+        <v>7057428</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127669031</v>
+        <v>127669023</v>
       </c>
       <c r="B7" t="n">
-        <v>57673</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1220,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466875</v>
+        <v>466691</v>
       </c>
       <c r="R7" t="n">
-        <v>7057276</v>
+        <v>7057419</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127669036</v>
+        <v>127669024</v>
       </c>
       <c r="B8" t="n">
-        <v>57673</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466984</v>
+        <v>466688</v>
       </c>
       <c r="R8" t="n">
-        <v>7057198</v>
+        <v>7057402</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127669021</v>
+        <v>127669025</v>
       </c>
       <c r="B9" t="n">
-        <v>57673</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1424,10 +1424,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466659</v>
+        <v>466688</v>
       </c>
       <c r="R9" t="n">
-        <v>7057412</v>
+        <v>7057397</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127669044</v>
+        <v>127669026</v>
       </c>
       <c r="B10" t="n">
-        <v>79032</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1502,21 +1502,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1526,10 +1526,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466937</v>
+        <v>466747</v>
       </c>
       <c r="R10" t="n">
-        <v>7057122</v>
+        <v>7057440</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127669039</v>
+        <v>127669027</v>
       </c>
       <c r="B11" t="n">
-        <v>57673</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1628,10 +1628,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466611</v>
+        <v>466891</v>
       </c>
       <c r="R11" t="n">
-        <v>7057193</v>
+        <v>7057348</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127669030</v>
+        <v>127669028</v>
       </c>
       <c r="B12" t="n">
-        <v>57673</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466857</v>
+        <v>466893</v>
       </c>
       <c r="R12" t="n">
-        <v>7057265</v>
+        <v>7057337</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1800,7 +1800,7 @@
         <v>127669029</v>
       </c>
       <c r="B13" t="n">
-        <v>57673</v>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127669020</v>
+        <v>127669030</v>
       </c>
       <c r="B14" t="n">
-        <v>57673</v>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1934,10 +1934,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>466669</v>
+        <v>466857</v>
       </c>
       <c r="R14" t="n">
-        <v>7057344</v>
+        <v>7057265</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127669023</v>
+        <v>127669031</v>
       </c>
       <c r="B15" t="n">
-        <v>57673</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,10 +2036,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466691</v>
+        <v>466875</v>
       </c>
       <c r="R15" t="n">
-        <v>7057419</v>
+        <v>7057276</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2076,7 +2076,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127669043</v>
+        <v>127669032</v>
       </c>
       <c r="B16" t="n">
-        <v>79032</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2114,21 +2114,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2138,10 +2138,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467172</v>
+        <v>467013</v>
       </c>
       <c r="R16" t="n">
-        <v>7057297</v>
+        <v>7057305</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127669028</v>
+        <v>127669033</v>
       </c>
       <c r="B17" t="n">
-        <v>57673</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466893</v>
+        <v>467084</v>
       </c>
       <c r="R17" t="n">
-        <v>7057337</v>
+        <v>7057443</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127669032</v>
+        <v>127669034</v>
       </c>
       <c r="B18" t="n">
-        <v>57673</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2342,10 +2342,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>467013</v>
+        <v>467117</v>
       </c>
       <c r="R18" t="n">
-        <v>7057305</v>
+        <v>7057269</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127669027</v>
+        <v>127669035</v>
       </c>
       <c r="B19" t="n">
-        <v>57673</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2444,10 +2444,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466891</v>
+        <v>467077</v>
       </c>
       <c r="R19" t="n">
-        <v>7057348</v>
+        <v>7057257</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127669037</v>
+        <v>127669036</v>
       </c>
       <c r="B20" t="n">
-        <v>57673</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2546,10 +2546,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466828</v>
+        <v>466984</v>
       </c>
       <c r="R20" t="n">
-        <v>7057181</v>
+        <v>7057198</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2613,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127669024</v>
+        <v>127669037</v>
       </c>
       <c r="B21" t="n">
-        <v>57673</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2648,10 +2648,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466688</v>
+        <v>466828</v>
       </c>
       <c r="R21" t="n">
-        <v>7057402</v>
+        <v>7057181</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2715,10 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127669041</v>
+        <v>127669038</v>
       </c>
       <c r="B22" t="n">
-        <v>57673</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2750,10 +2750,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466603</v>
+        <v>466664</v>
       </c>
       <c r="R22" t="n">
-        <v>7057208</v>
+        <v>7057206</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127669025</v>
+        <v>127669039</v>
       </c>
       <c r="B23" t="n">
-        <v>57673</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2852,10 +2852,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466688</v>
+        <v>466611</v>
       </c>
       <c r="R23" t="n">
-        <v>7057397</v>
+        <v>7057193</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2892,7 +2892,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2919,10 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127669022</v>
+        <v>127669040</v>
       </c>
       <c r="B24" t="n">
-        <v>57673</v>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2954,10 +2954,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>466685</v>
+        <v>466606</v>
       </c>
       <c r="R24" t="n">
-        <v>7057428</v>
+        <v>7057202</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,10 +3021,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127669033</v>
+        <v>127669041</v>
       </c>
       <c r="B25" t="n">
-        <v>57673</v>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3056,10 +3056,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>467084</v>
+        <v>466603</v>
       </c>
       <c r="R25" t="n">
-        <v>7057443</v>
+        <v>7057208</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3123,10 +3123,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127669026</v>
+        <v>127669042</v>
       </c>
       <c r="B26" t="n">
-        <v>57673</v>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3158,10 +3158,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466747</v>
+        <v>466580</v>
       </c>
       <c r="R26" t="n">
-        <v>7057440</v>
+        <v>7057216</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 36011-2025 artfynd.xlsx
+++ b/artfynd/A 36011-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127669043</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127669044</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127669020</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127669021</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127669022</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127669023</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1386,6 +1421,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127669024</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1488,6 +1528,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127669025</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1590,6 +1635,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127669026</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1692,6 +1742,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127669027</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1794,6 +1849,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127669028</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1896,6 +1956,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127669029</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1998,6 +2063,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127669030</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2100,6 +2170,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127669031</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2202,6 +2277,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127669032</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2304,6 +2384,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127669033</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2406,6 +2491,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127669034</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2508,6 +2598,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127669035</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2610,6 +2705,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127669036</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2712,6 +2812,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127669037</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2814,6 +2919,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127669038</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2916,6 +3026,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127669039</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3018,6 +3133,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127669040</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3120,6 +3240,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127669041</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3222,8 +3347,40 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127669042</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>